--- a/codespace/DetroitRiverCase/results/ch4_fw2_stress_profile.xlsx
+++ b/codespace/DetroitRiverCase/results/ch4_fw2_stress_profile.xlsx
@@ -470,16 +470,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2887618353702303</v>
+        <v>0.2943653605201318</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2887618353702303</v>
+        <v>0.2943653605201318</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2887619493874255</v>
+        <v>0.2943653613430097</v>
       </c>
       <c r="F2" t="n">
-        <v>1.357651450151209e-07</v>
+        <v>1.680288685967923e-09</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08621513022253674</v>
+        <v>0.08136607427318598</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08621513022253674</v>
+        <v>0.08136607427318598</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0862334164787672</v>
+        <v>0.08136648092682908</v>
       </c>
       <c r="F3" t="n">
-        <v>2.575944900494453e-05</v>
+        <v>2.882301368120621e-06</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0554311142684376</v>
+        <v>0.04618359410965732</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0554311142684376</v>
+        <v>0.04618359410965732</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05890874284349558</v>
+        <v>0.0461916448842444</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003508328013279036</v>
+        <v>1.86187333632501e-05</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04925290371482224</v>
+        <v>0.03451288321388205</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04925290371482224</v>
+        <v>0.03451288321388205</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04927407122745169</v>
+        <v>0.03451338969181496</v>
       </c>
       <c r="F5" t="n">
-        <v>2.746916947225092e-05</v>
+        <v>6.506886951876401e-06</v>
       </c>
     </row>
     <row r="6">
@@ -558,16 +558,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04268561376704739</v>
+        <v>0.02682343611070813</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04268561376704739</v>
+        <v>0.02682343611070813</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04269312872239998</v>
+        <v>0.02683169212314559</v>
       </c>
       <c r="F6" t="n">
-        <v>9.414160966912666e-06</v>
+        <v>1.33837565125354e-05</v>
       </c>
     </row>
     <row r="7">
@@ -580,16 +580,16 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3173938279086821</v>
+        <v>0.3172965020604847</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3173938279086821</v>
+        <v>0.3172965020604847</v>
       </c>
       <c r="E7" t="n">
-        <v>0.317393827924164</v>
+        <v>0.3172965078635093</v>
       </c>
       <c r="F7" t="n">
-        <v>1.922648987850994e-06</v>
+        <v>3.862534793874772e-05</v>
       </c>
     </row>
     <row r="8">
@@ -602,16 +602,16 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1521196397879057</v>
+        <v>0.1512313706850802</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1521196397879057</v>
+        <v>0.1512313706850802</v>
       </c>
       <c r="E8" t="n">
-        <v>0.152120052629396</v>
+        <v>0.1512316972764406</v>
       </c>
       <c r="F8" t="n">
-        <v>1.011885541413182e-06</v>
+        <v>7.22536783370753e-06</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>0.07810512841790582</v>
+        <v>0.07451228282651792</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07810512841790582</v>
+        <v>0.07451228282651792</v>
       </c>
       <c r="E9" t="n">
-        <v>0.07811420595174966</v>
+        <v>0.07451640872995827</v>
       </c>
       <c r="F9" t="n">
-        <v>1.795231757696636e-05</v>
+        <v>6.32744999695678e-06</v>
       </c>
     </row>
     <row r="10">
@@ -646,16 +646,16 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05671088640175866</v>
+        <v>0.05231518240607132</v>
       </c>
       <c r="D10" t="n">
-        <v>0.05671088640175866</v>
+        <v>0.05231518240607132</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05671635980163435</v>
+        <v>0.05231927747095708</v>
       </c>
       <c r="F10" t="n">
-        <v>1.03267407393498e-05</v>
+        <v>5.309674023588895e-06</v>
       </c>
     </row>
     <row r="11">
@@ -668,16 +668,16 @@
         <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04607248601880973</v>
+        <v>0.04075104303324562</v>
       </c>
       <c r="D11" t="n">
-        <v>0.04607248601880973</v>
+        <v>0.04075104303324562</v>
       </c>
       <c r="E11" t="n">
-        <v>0.04608281880984962</v>
+        <v>0.04076230988942613</v>
       </c>
       <c r="F11" t="n">
-        <v>2.428950308047684e-05</v>
+        <v>2.681134637542298e-05</v>
       </c>
     </row>
     <row r="12">
@@ -690,16 +690,16 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2601014894359347</v>
+        <v>0.2610174812872342</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2601014894359347</v>
+        <v>0.2610174812872342</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2601017137920185</v>
+        <v>0.2610460837072883</v>
       </c>
       <c r="F12" t="n">
-        <v>2.265380468768896e-07</v>
+        <v>2.874490337972935e-05</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1319956136146898</v>
+        <v>0.1200138708563828</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1319956136146898</v>
+        <v>0.1200138708563828</v>
       </c>
       <c r="E13" t="n">
-        <v>0.131995864074393</v>
+        <v>0.1200145638040309</v>
       </c>
       <c r="F13" t="n">
-        <v>1.224623605466935e-06</v>
+        <v>1.143179707244202e-06</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0851496114229114</v>
+        <v>0.06610243462690057</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0851496114229114</v>
+        <v>0.06610243462690057</v>
       </c>
       <c r="E14" t="n">
-        <v>0.08548518810977843</v>
+        <v>0.06612236381096058</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0003803270695317273</v>
+        <v>3.704455497692549e-05</v>
       </c>
     </row>
     <row r="15">
@@ -756,16 +756,16 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06892525083971253</v>
+        <v>0.04176862678713629</v>
       </c>
       <c r="D15" t="n">
-        <v>0.06892525083971253</v>
+        <v>0.04176862678713629</v>
       </c>
       <c r="E15" t="n">
-        <v>0.07124578896885315</v>
+        <v>0.04177591433915439</v>
       </c>
       <c r="F15" t="n">
-        <v>0.002351522439862558</v>
+        <v>2.98624884014706e-05</v>
       </c>
     </row>
     <row r="16">
@@ -778,16 +778,16 @@
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>0.06063106710124018</v>
+        <v>0.03010792015118075</v>
       </c>
       <c r="D16" t="n">
-        <v>0.06063106710124018</v>
+        <v>0.03010792015118075</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06063804167199356</v>
+        <v>0.03011320216446061</v>
       </c>
       <c r="F16" t="n">
-        <v>1.180369729195108e-05</v>
+        <v>1.760062267651408e-05</v>
       </c>
     </row>
   </sheetData>
